--- a/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.6.xlsx
+++ b/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96881AAB-09A8-4726-B8D5-483088A6D6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A8E6F0-AEE8-491F-91CC-EABCAD1B2B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="SIM3_比較" sheetId="2" r:id="rId2"/>
     <sheet name="SIM考え方" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1490,36 +1490,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <extLst>
@@ -1535,6 +1505,36 @@
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1985,7 +1985,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="136" t="s">
+      <c r="A8" s="135" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -2018,7 +2018,7 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="139"/>
+      <c r="A9" s="136"/>
       <c r="B9" s="19" t="s">
         <v>14</v>
       </c>
@@ -2048,7 +2048,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="136" t="s">
+      <c r="A10" s="135" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -2074,7 +2074,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="139"/>
+      <c r="A11" s="136"/>
       <c r="B11" s="19" t="s">
         <v>24</v>
       </c>
@@ -2106,10 +2106,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="144" t="s">
+      <c r="A13" s="145" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="134"/>
+      <c r="B13" s="138"/>
       <c r="C13" s="92"/>
       <c r="D13" s="13" t="s">
         <v>28</v>
@@ -2152,7 +2152,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="133" t="s">
+      <c r="A14" s="137" t="s">
         <v>39</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -2185,7 +2185,7 @@
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="140"/>
+      <c r="A15" s="141"/>
       <c r="B15" s="20" t="s">
         <v>41</v>
       </c>
@@ -2228,7 +2228,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="139"/>
+      <c r="A16" s="136"/>
       <c r="B16" s="20" t="s">
         <v>45</v>
       </c>
@@ -2271,32 +2271,32 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="133" t="s">
+      <c r="A17" s="137" t="s">
         <v>48</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="97"/>
-      <c r="D17" s="145" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" s="146" t="b">
+      <c r="D17" s="133" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="134" t="b">
         <v>0</v>
       </c>
       <c r="K17" s="14" t="s">
@@ -2316,30 +2316,30 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="140"/>
+      <c r="A18" s="141"/>
       <c r="B18" s="8" t="s">
         <v>54</v>
       </c>
       <c r="C18" s="97"/>
-      <c r="D18" s="145" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="146" t="b">
+      <c r="D18" s="133" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="134" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="146" t="b">
+      <c r="F18" s="134" t="b">
         <v>1</v>
       </c>
-      <c r="G18" s="146" t="b">
+      <c r="G18" s="134" t="b">
         <v>1</v>
       </c>
-      <c r="H18" s="146" t="b">
+      <c r="H18" s="134" t="b">
         <v>1</v>
       </c>
-      <c r="I18" s="146" t="b">
+      <c r="I18" s="134" t="b">
         <v>1</v>
       </c>
-      <c r="J18" s="146" t="b">
+      <c r="J18" s="134" t="b">
         <v>1</v>
       </c>
       <c r="K18" s="14" t="s">
@@ -2380,30 +2380,30 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="140"/>
+      <c r="A19" s="141"/>
       <c r="B19" s="8" t="s">
         <v>57</v>
       </c>
       <c r="C19" s="97"/>
-      <c r="D19" s="145" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" s="146" t="b">
+      <c r="D19" s="133" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="134" t="b">
         <v>0</v>
       </c>
       <c r="K19" s="14"/>
@@ -2441,30 +2441,30 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="140"/>
+      <c r="A20" s="141"/>
       <c r="B20" s="8" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="97"/>
-      <c r="D20" s="145" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" s="146" t="b">
+      <c r="D20" s="133" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="134" t="b">
         <v>0</v>
       </c>
       <c r="K20" s="14"/>
@@ -2476,30 +2476,30 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="139"/>
+      <c r="A21" s="136"/>
       <c r="B21" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C21" s="97"/>
-      <c r="D21" s="145" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" s="146" t="b">
+      <c r="D21" s="133" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="134" t="b">
         <v>0</v>
       </c>
       <c r="K21" s="14" t="s">
@@ -2519,7 +2519,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="141" t="s">
+      <c r="A22" s="140" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -2571,7 +2571,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="140"/>
+      <c r="A23" s="141"/>
       <c r="B23" s="6" t="s">
         <v>54</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="140"/>
+      <c r="A24" s="141"/>
       <c r="B24" s="6" t="s">
         <v>57</v>
       </c>
@@ -2677,7 +2677,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="139"/>
+      <c r="A25" s="136"/>
       <c r="B25" s="6" t="s">
         <v>70</v>
       </c>
@@ -2725,31 +2725,37 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="133" t="s">
+      <c r="A26" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="134"/>
+      <c r="B26" s="138"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>50</v>
       </c>
       <c r="E26" s="46">
         <f>SUM(E22:E25)+E14*0.015*0.62</f>
+        <v>81.777224999999987</v>
       </c>
       <c r="F26" s="46">
         <f>SUM(F22:F25)+F14*0.015*0.81</f>
+        <v>105.20280000000001</v>
       </c>
       <c r="G26" s="46">
         <f>SUM(G22:G25)+G14*0.015*0.93</f>
+        <v>119.87932499999999</v>
       </c>
       <c r="H26" s="46">
         <f>SUM(H22:H25)+H14*0.015*1</f>
+        <v>131.30375000000001</v>
       </c>
       <c r="I26" s="46">
         <f>SUM(I22:I25)+I14*0.015*1.03</f>
+        <v>131.4344375</v>
       </c>
       <c r="J26" s="46">
         <f>SUM(J22:J25)+J14*0.015*1.05</f>
+        <v>139.29693750000001</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
@@ -2769,10 +2775,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="133" t="s">
+      <c r="A27" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="134"/>
+      <c r="B27" s="138"/>
       <c r="C27" s="23"/>
       <c r="D27" s="104">
         <v>0</v>
@@ -2816,37 +2822,37 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="143" t="s">
+      <c r="A28" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="134"/>
+      <c r="B28" s="138"/>
       <c r="C28" s="98"/>
       <c r="D28" s="103">
         <v>0</v>
       </c>
       <c r="E28" s="49">
         <f t="shared" ref="E28:J28" si="0">+D28+E26</f>
-        <v>101.01892500000001</v>
+        <v>81.777224999999987</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" si="0"/>
-        <v>230.975325</v>
+        <v>186.98002500000001</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="0"/>
-        <v>379.06155000000001</v>
+        <v>306.85935000000001</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="0"/>
-        <v>541.26030000000003</v>
+        <v>438.16309999999999</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="0"/>
-        <v>703.62048750000008</v>
+        <v>569.59753750000004</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="0"/>
-        <v>875.69317500000011</v>
+        <v>708.89447500000006</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -2869,34 +2875,34 @@
       <c r="A29" s="142" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="134"/>
+      <c r="B29" s="138"/>
       <c r="C29" s="99"/>
       <c r="D29" s="105">
         <v>0</v>
       </c>
       <c r="E29" s="50">
         <f t="shared" ref="E29:J29" si="1">+E28*(1-E27)</f>
-        <v>60.00524145</v>
+        <v>48.57567164999999</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" si="1"/>
-        <v>140.663972925</v>
+        <v>113.87083522500001</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="1"/>
-        <v>235.7762841</v>
+        <v>190.86651570000001</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="1"/>
-        <v>345.32407140000004</v>
+        <v>279.54805779999998</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="1"/>
-        <v>451.02073248750008</v>
+        <v>365.11202153750003</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="1"/>
-        <v>574.45472280000013</v>
+        <v>465.03477560000005</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -2910,10 +2916,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="139" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="134"/>
+      <c r="B30" s="138"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -2952,10 +2958,10 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="133" t="s">
+      <c r="A31" s="137" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="134"/>
+      <c r="B31" s="138"/>
       <c r="C31" s="23"/>
       <c r="D31" s="105">
         <f>+D30*D29*0.41*0.07</f>
@@ -2963,27 +2969,27 @@
       </c>
       <c r="E31" s="61">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>21.928277032133483</v>
+        <v>17.751462359346149</v>
       </c>
       <c r="F31" s="61">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>51.404152240769356</v>
+        <v>41.612885147289482</v>
       </c>
       <c r="G31" s="61">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>86.161934364682239</v>
+        <v>69.750137342838002</v>
       </c>
       <c r="H31" s="61">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>100.95600611600831</v>
+        <v>81.726290665340059</v>
       </c>
       <c r="I31" s="61">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>131.85658226157065</v>
+        <v>106.74104278317625</v>
       </c>
       <c r="J31" s="61">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>167.94269299920768</v>
+        <v>135.95360861840618</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -2994,10 +3000,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="139" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="134"/>
+      <c r="B32" s="138"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -3041,37 +3047,37 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="133" t="s">
+      <c r="A33" s="137" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="134"/>
+      <c r="B33" s="138"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
       </c>
       <c r="E33" s="61">
         <f>+E29*E32*$P$26*$P$27*$P$28*$P$36</f>
-        <v>15.286539277208433</v>
+        <v>12.374817510121112</v>
       </c>
       <c r="F33" s="61">
         <f>+F29*F32*$P$26*$P$27*$P$28*$P$36</f>
-        <v>35.834625360151712</v>
+        <v>29.008982434408534</v>
       </c>
       <c r="G33" s="61">
         <f>+G29*G32*$P$26*$P$27*$P$28*$P$36</f>
-        <v>60.064810013840962</v>
+        <v>48.623893820728405</v>
       </c>
       <c r="H33" s="61">
         <f>+H29*H32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
-        <v>70.377985032794228</v>
+        <v>56.972654550357234</v>
       </c>
       <c r="I33" s="61">
         <f>+I29*I32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
-        <v>91.919252057344934</v>
+        <v>74.41082309404112</v>
       </c>
       <c r="J33" s="61">
         <f>+J29*J32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
-        <v>117.07543502348611</v>
+        <v>94.775352161869691</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -3090,7 +3096,7 @@
       <c r="A34" s="142" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="134"/>
+      <c r="B34" s="138"/>
       <c r="C34" s="99"/>
       <c r="D34" s="105">
         <f>+D29*D30</f>
@@ -3098,27 +3104,27 @@
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E29*E32*$P$28</f>
-        <v>312.02725554</v>
+        <v>252.59349257999997</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F29*F32*$P$28</f>
-        <v>731.45265921000009</v>
+        <v>592.12834317000011</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G29*G32*$P$28</f>
-        <v>1226.0366773200001</v>
+        <v>992.5058816400001</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H29*H32*$P$28*$Q$28</f>
-        <v>1436.5481370240004</v>
+        <v>1162.9199204480001</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I29*I32*$P$28*$Q$28</f>
-        <v>1876.2462471480005</v>
+        <v>1518.8660095960004</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J29*J32*$P$28*$Q$28</f>
-        <v>2389.7316468480008</v>
+        <v>1934.5446664960004</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -3137,7 +3143,7 @@
       <c r="A35" s="142" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="134"/>
+      <c r="B35" s="138"/>
       <c r="C35" s="99"/>
       <c r="D35" s="106">
         <f>+D31*1.02</f>
@@ -3145,27 +3151,27 @@
       </c>
       <c r="E35" s="50">
         <f t="shared" ref="E35:J35" si="2">+E31+E33+1.05*(E31+E33)+E29*0.3*2</f>
-        <v>112.29351830415092</v>
+        <v>90.904276722407872</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" si="2"/>
-        <v>263.23787783688817</v>
+        <v>213.0973296774809</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="2"/>
-        <v>441.23059643597253</v>
+        <v>357.18667330531116</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="2"/>
-        <v>558.42912469504518</v>
+        <v>452.06167237217937</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="2"/>
-        <v>729.35289984627707</v>
+        <v>590.42853797079556</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="2"/>
-        <v>928.95999612652224</v>
+        <v>752.01523495956553</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -3184,7 +3190,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="138" t="s">
+      <c r="A36" s="143" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="6" t="str">
@@ -3197,25 +3203,31 @@
       </c>
       <c r="E36" s="108">
         <f>ROUND(E14*0.015*0.62,0)</f>
+        <v>58</v>
       </c>
       <c r="F36" s="108">
         <f>ROUND(F14*0.015*0.81,0)</f>
+        <v>74</v>
       </c>
       <c r="G36" s="108">
         <f>ROUND(G14*0.015*0.93,0)</f>
+        <v>85</v>
       </c>
       <c r="H36" s="108">
         <f>ROUND(H14*0.015*1,0)</f>
+        <v>93</v>
       </c>
       <c r="I36" s="108">
         <f>ROUND(I14*0.015*1.03,0)</f>
+        <v>93</v>
       </c>
       <c r="J36" s="108">
         <f>ROUND(J14*0.015*1.05,0)</f>
+        <v>98</v>
       </c>
       <c r="K36" s="112">
         <f>SUM(E36:J36)</f>
-        <v>668</v>
+        <v>501</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="67" t="s">
@@ -3231,7 +3243,7 @@
       <c r="Q36" s="71"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="139"/>
+      <c r="A37" s="136"/>
       <c r="B37" s="6" t="str">
         <f>+C9</f>
         <v>求人応募（LINE経由）</v>
@@ -3241,26 +3253,26 @@
         <v>0</v>
       </c>
       <c r="E37" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G37" s="108">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H37" s="108">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I37" s="108">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J37" s="108">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K37" s="112">
         <f>SUM(E37:J37)</f>
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="67" t="s">
@@ -3268,7 +3280,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="138" t="s">
+      <c r="A38" s="143" t="s">
         <v>19</v>
       </c>
       <c r="B38" s="6" t="str">
@@ -3310,7 +3322,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="139"/>
+      <c r="A39" s="136"/>
       <c r="B39" s="6" t="str">
         <f>+C11</f>
         <v>-</v>
@@ -3350,10 +3362,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="136" t="s">
+      <c r="A40" s="135" t="s">
         <v>100</v>
       </c>
-      <c r="B40" s="134"/>
+      <c r="B40" s="138"/>
       <c r="C40" s="94"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="3">+D37</f>
@@ -3361,19 +3373,19 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="3"/>
@@ -3385,7 +3397,7 @@
       </c>
       <c r="K40" s="112">
         <f>SUM(E40:J40)</f>
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="L40" s="7"/>
       <c r="N40" t="s">
@@ -3403,27 +3415,27 @@
       </c>
       <c r="E41" s="18">
         <f t="shared" si="4"/>
-        <v>3.5620933963132762E-2</v>
+        <v>3.3001747642314186E-2</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" si="4"/>
-        <v>2.6591917764727826E-2</v>
+        <v>2.3463456851230434E-2</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="4"/>
-        <v>2.2663886142018964E-2</v>
+        <v>2.2397252187406971E-2</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="4"/>
-        <v>2.1488850544020475E-2</v>
+        <v>2.433296311602319E-2</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="4"/>
-        <v>1.7824019076005539E-2</v>
+        <v>2.2017905917418614E-2</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="4"/>
-        <v>1.6147089285378693E-2</v>
+        <v>1.9946404411350153E-2</v>
       </c>
       <c r="N41" s="67" t="s">
         <v>103</v>
@@ -3451,10 +3463,10 @@
       </c>
     </row>
     <row r="44" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="133" t="s">
+      <c r="A44" s="137" t="s">
         <v>107</v>
       </c>
-      <c r="B44" s="134"/>
+      <c r="B44" s="138"/>
       <c r="C44" s="100"/>
       <c r="D44" s="16" t="s">
         <v>50</v>
@@ -3487,10 +3499,10 @@
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="133" t="s">
+      <c r="A45" s="137" t="s">
         <v>108</v>
       </c>
-      <c r="B45" s="134"/>
+      <c r="B45" s="138"/>
       <c r="C45" s="101">
         <f>+SUM(C65:C72)</f>
         <v>0</v>
@@ -3527,137 +3539,137 @@
       <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="137" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="134"/>
+      <c r="B46" s="138"/>
       <c r="C46" s="100"/>
       <c r="D46" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="7">+SUM(E65:E67)/(E28-D28)</f>
-        <v>296.97405708880785</v>
+        <v>366.85030581558624</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="7"/>
-        <v>230.84665318522218</v>
+        <v>285.16351275821552</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="7"/>
-        <v>202.58467659635457</v>
+        <v>250.25165932490862</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="7"/>
-        <v>184.95826879060411</v>
+        <v>228.4778614472169</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="7"/>
-        <v>184.77436163345149</v>
+        <v>228.250682017793</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="7"/>
-        <v>174.34492618126856</v>
+        <v>215.36726175333177</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="133" t="s">
+      <c r="A47" s="137" t="s">
         <v>110</v>
       </c>
-      <c r="B47" s="134"/>
+      <c r="B47" s="138"/>
       <c r="C47" s="100"/>
       <c r="D47" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:J47" si="8">+E51/E35</f>
-        <v>2092.7298703340498</v>
+        <v>2585.1368986479442</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="8"/>
-        <v>892.72866781586276</v>
+        <v>1102.7824720078304</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="8"/>
-        <v>532.6013243374457</v>
+        <v>657.91928300507982</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="8"/>
-        <v>420.82332315373435</v>
+        <v>519.84057566049546</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="8"/>
-        <v>322.20342175856166</v>
+        <v>398.01599158410568</v>
       </c>
       <c r="J47" s="28">
         <f t="shared" si="8"/>
-        <v>252.97106547093287</v>
+        <v>312.49366911115243</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="133" t="s">
+      <c r="A48" s="137" t="s">
         <v>111</v>
       </c>
-      <c r="B48" s="134"/>
+      <c r="B48" s="138"/>
       <c r="C48" s="100"/>
       <c r="D48" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="9">+SUM(E36:E39)/E35</f>
-        <v>0.72132391275343843</v>
+        <v>0.67103553539372174</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="9"/>
-        <v>0.40267761186587853</v>
+        <v>0.37072261824944086</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="9"/>
-        <v>0.27876579954683328</v>
+        <v>0.26036805667860607</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="9"/>
-        <v>0.24354030616556541</v>
+        <v>0.23005710582421923</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="9"/>
-        <v>0.18783773949328914</v>
+        <v>0.17953061748049023</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="9"/>
-        <v>0.15716500237768596</v>
+        <v>0.15026291323217117</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="136" t="s">
+      <c r="A49" s="135" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="134"/>
+      <c r="B49" s="138"/>
       <c r="C49" s="102"/>
       <c r="D49" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E37:E39),0)</f>
-        <v>58750</v>
+        <v>78333.333333333328</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="10">+IFERROR(F51/SUM(F37:F39),0)</f>
-        <v>33571.428571428572</v>
+        <v>47000</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="10"/>
-        <v>23500</v>
+        <v>29375</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="10"/>
-        <v>19583.333333333332</v>
+        <v>21363.636363636364</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="10"/>
@@ -3671,10 +3683,10 @@
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="136" t="s">
+      <c r="A50" s="135" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="134"/>
+      <c r="B50" s="138"/>
       <c r="C50" s="102"/>
       <c r="D50" s="62" t="s">
         <v>50</v>
@@ -3707,10 +3719,10 @@
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="137" t="s">
+      <c r="A51" s="146" t="s">
         <v>114</v>
       </c>
-      <c r="B51" s="134"/>
+      <c r="B51" s="138"/>
       <c r="C51" s="107">
         <f>+C45</f>
         <v>0</v>
@@ -3764,10 +3776,10 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="133" t="s">
+      <c r="A54" s="137" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="134"/>
+      <c r="B54" s="138"/>
       <c r="C54" s="93"/>
       <c r="D54" s="28">
         <f t="shared" ref="D54:J54" si="13">+D75*D76</f>
@@ -3801,10 +3813,10 @@
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="133" t="s">
+      <c r="A55" s="137" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="134"/>
+      <c r="B55" s="138"/>
       <c r="C55" s="93"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
@@ -3838,135 +3850,135 @@
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="133" t="s">
+      <c r="A56" s="137" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="134"/>
+      <c r="B56" s="138"/>
       <c r="C56" s="93"/>
       <c r="D56" s="39" t="s">
         <v>50</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" ref="E56:J56" si="15">+SUM(E65:E67)/(E28-D28)</f>
-        <v>296.97405708880785</v>
+        <v>366.85030581558624</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" si="15"/>
-        <v>230.84665318522218</v>
+        <v>285.16351275821552</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="15"/>
-        <v>202.58467659635457</v>
+        <v>250.25165932490862</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="15"/>
-        <v>184.95826879060411</v>
+        <v>228.4778614472169</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="15"/>
-        <v>184.77436163345149</v>
+        <v>228.250682017793</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="15"/>
-        <v>174.34492618126856</v>
+        <v>215.36726175333177</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="133" t="s">
+      <c r="A57" s="137" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="134"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="93"/>
       <c r="D57" s="39" t="s">
         <v>50</v>
       </c>
       <c r="E57" s="28">
         <f t="shared" ref="E57:J57" si="16">+E61/E35</f>
-        <v>2092.7298703340498</v>
+        <v>2585.1368986479442</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" si="16"/>
-        <v>892.72866781586276</v>
+        <v>1102.7824720078304</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="16"/>
-        <v>532.6013243374457</v>
+        <v>657.91928300507982</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="16"/>
-        <v>420.82332315373435</v>
+        <v>519.84057566049546</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="16"/>
-        <v>322.20342175856166</v>
+        <v>398.01599158410568</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="16"/>
-        <v>252.97106547093287</v>
+        <v>312.49366911115243</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="133" t="s">
+      <c r="A58" s="137" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="134"/>
+      <c r="B58" s="138"/>
       <c r="C58" s="93"/>
       <c r="D58" s="39" t="s">
         <v>50</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="17">+SUM(E36:E39)/E35</f>
-        <v>0.72132391275343843</v>
+        <v>0.67103553539372174</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="17"/>
-        <v>0.40267761186587853</v>
+        <v>0.37072261824944086</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="17"/>
-        <v>0.27876579954683328</v>
+        <v>0.26036805667860607</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="17"/>
-        <v>0.24354030616556541</v>
+        <v>0.23005710582421923</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="17"/>
-        <v>0.18783773949328914</v>
+        <v>0.17953061748049023</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="17"/>
-        <v>0.15716500237768596</v>
+        <v>0.15026291323217117</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="136" t="s">
+      <c r="A59" s="135" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="134"/>
+      <c r="B59" s="138"/>
       <c r="C59" s="94"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f t="shared" ref="E59:J59" si="18">+IFERROR(E55/E40,0)</f>
-        <v>58750</v>
+        <v>78333.333333333328</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" si="18"/>
-        <v>33571.428571428572</v>
+        <v>47000</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="18"/>
-        <v>23500</v>
+        <v>29375</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="18"/>
-        <v>19583.333333333332</v>
+        <v>21363.636363636364</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="18"/>
@@ -3980,10 +3992,10 @@
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="136" t="s">
+      <c r="A60" s="135" t="s">
         <v>113</v>
       </c>
-      <c r="B60" s="134"/>
+      <c r="B60" s="138"/>
       <c r="C60" s="94"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -3996,10 +4008,10 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="137" t="s">
+      <c r="A61" s="146" t="s">
         <v>114</v>
       </c>
-      <c r="B61" s="134"/>
+      <c r="B61" s="138"/>
       <c r="C61" s="95"/>
       <c r="D61" s="40">
         <f>+D55</f>
@@ -4446,6 +4458,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A49:B49"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A33:B33"/>
@@ -4462,25 +4493,6 @@
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A36:A37"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4576,11 +4588,11 @@
       </c>
       <c r="D6" s="84">
         <f>+'SIM3_LINE登録2%'!G28</f>
-        <v>379.06155000000001</v>
+        <v>306.85935000000001</v>
       </c>
       <c r="E6" s="84">
         <f>+'SIM3_LINE登録2%'!J28</f>
-        <v>875.69317500000011</v>
+        <v>708.89447500000006</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -4614,11 +4626,11 @@
       </c>
       <c r="D8" s="10">
         <f>+'SIM3_LINE登録2%'!G29</f>
-        <v>235.7762841</v>
+        <v>190.86651570000001</v>
       </c>
       <c r="E8" s="10">
         <f>+'SIM3_LINE登録2%'!J29</f>
-        <v>574.45472280000013</v>
+        <v>465.03477560000005</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -4641,11 +4653,11 @@
       </c>
       <c r="D10" s="10">
         <f>+'SIM3_LINE登録2%'!G34</f>
-        <v>1226.0366773200001</v>
+        <v>992.5058816400001</v>
       </c>
       <c r="E10" s="10">
         <f>+'SIM3_LINE登録2%'!J34</f>
-        <v>2389.7316468480008</v>
+        <v>1934.5446664960004</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -4660,11 +4672,11 @@
       </c>
       <c r="D11" s="10">
         <f>+'SIM3_LINE登録2%'!G35</f>
-        <v>441.23059643597253</v>
+        <v>357.18667330531116</v>
       </c>
       <c r="E11" s="10">
         <f>+'SIM3_LINE登録2%'!J35</f>
-        <v>928.95999612652224</v>
+        <v>752.01523495956553</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -4679,11 +4691,11 @@
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>532.6013243374457</v>
+        <v>657.91928300507982</v>
       </c>
       <c r="E12" s="28">
         <f>+E4/E11</f>
-        <v>252.97106547093287</v>
+        <v>312.49366911115243</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -4698,11 +4710,11 @@
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>532.6013243374457</v>
+        <v>657.91928300507982</v>
       </c>
       <c r="E13" s="28">
         <f>+E5/E11</f>
-        <v>252.97106547093287</v>
+        <v>312.49366911115243</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -4750,7 +4762,7 @@
       </c>
       <c r="D16" s="84">
         <f>+D18</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E16" s="84">
         <f>+E18</f>
@@ -4778,11 +4790,11 @@
       </c>
       <c r="D17" s="84">
         <f>+'SIM3_LINE登録2%'!G36</f>
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="E17" s="84">
         <f>+'SIM3_LINE登録2%'!J36</f>
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -4818,7 +4830,7 @@
       </c>
       <c r="D18" s="84">
         <f>+'SIM3_LINE登録2%'!G37</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E18" s="84">
         <f>+'SIM3_LINE登録2%'!J37</f>
@@ -4920,7 +4932,7 @@
       </c>
       <c r="D22" s="87">
         <f>+IFERROR(D4/D16,"--")</f>
-        <v>23500</v>
+        <v>29375</v>
       </c>
       <c r="E22" s="87">
         <f>+IFERROR(E4/E16,"--")</f>
@@ -4944,7 +4956,7 @@
       </c>
       <c r="D23" s="87">
         <f>+IFERROR(D5/D16,"--")</f>
-        <v>23500</v>
+        <v>29375</v>
       </c>
       <c r="E23" s="87">
         <f>+IFERROR(E5/E16,"--")</f>
